--- a/public/template/template_santri.xlsx
+++ b/public/template/template_santri.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sukma Manggar SP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\php83\woowdoa\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A98ED2CE-8BF4-47B5-95BA-69D65F547FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181AD593-1B77-4ABC-BBB5-5F9893388B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BAD5E8CA-993F-4141-9A9E-5B2DEA23FB66}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>No</t>
   </si>
@@ -48,13 +48,25 @@
     <t>gender</t>
   </si>
   <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>parent_phone</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>tahun_ajaran</t>
+  </si>
+  <si>
     <t>address</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>email</t>
   </si>
 </sst>
 </file>
@@ -70,9 +82,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -110,20 +122,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -436,17 +448,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C180D986-5DED-4C5A-A064-24C7A0C9D38D}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.08984375" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -462,22 +477,38 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -485,8 +516,12 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -494,8 +529,12 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -503,8 +542,12 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -512,15 +555,10 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
